--- a/Material/2. Interviews & Surveys/Attribute Definition.xlsx
+++ b/Material/2. Interviews & Surveys/Attribute Definition.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\DSE_thesis\Material\2. Interviews &amp; Surveys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2015489-4BD5-411D-9955-359D0D2AFBE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903896E5-AFB6-4679-AD4A-63AC3B88E702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="824" activeTab="3" xr2:uid="{1010D4BD-99A2-4997-AD21-2857331DB82F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="824" activeTab="2" xr2:uid="{1010D4BD-99A2-4997-AD21-2857331DB82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Improvement" sheetId="9" r:id="rId1"/>
@@ -1608,7 +1608,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1715,9 +1715,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1726,6 +1723,18 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2137,68 +2146,68 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="37" t="s">
+      <c r="E2" s="36" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="36" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="E4" s="37" t="s">
+      <c r="E4" s="36" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="37" t="s">
+      <c r="A5" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="37" t="s">
+      <c r="C5" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="E5" s="37" t="s">
+      <c r="E5" s="36" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="37" t="s">
+      <c r="A6" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="37" t="s">
+      <c r="C6" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="E6" s="37" t="s">
+      <c r="E6" s="36" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="37" t="s">
+      <c r="A7" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="E7" s="37" t="s">
+      <c r="E7" s="36" t="s">
         <v>285</v>
       </c>
       <c r="F7" s="25" t="s">
@@ -2206,41 +2215,41 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="C8" s="36" t="s">
         <v>143</v>
       </c>
-      <c r="E8" s="37" t="s">
+      <c r="E8" s="36" t="s">
         <v>170</v>
       </c>
       <c r="F8" s="13"/>
     </row>
     <row r="9" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="C9" s="37" t="s">
+      <c r="C9" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="E9" s="37" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C10" s="37" t="s">
+      <c r="C10" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="E10" s="37" t="s">
+      <c r="E10" s="36" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C11" s="37" t="s">
+      <c r="C11" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="E11" s="37" t="s">
+      <c r="E11" s="36" t="s">
         <v>174</v>
       </c>
       <c r="F11" s="13"/>
@@ -4348,15 +4357,15 @@
   <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="63.77734375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="116.21875" customWidth="1"/>
+    <col min="1" max="1" width="63" style="7" customWidth="1"/>
+    <col min="2" max="2" width="63" style="42" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19" t="s">
+      <c r="A1" s="39" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="41" t="s">
         <v>222</v>
       </c>
     </row>
@@ -4364,7 +4373,7 @@
       <c r="A2" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="40" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4372,7 +4381,7 @@
       <c r="A3" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="40" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4380,7 +4389,7 @@
       <c r="A4" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="40" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4388,7 +4397,7 @@
       <c r="A5" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="29" t="s">
+      <c r="B5" s="40" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4396,7 +4405,7 @@
       <c r="A6" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B6" s="29" t="s">
+      <c r="B6" s="40" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4404,7 +4413,7 @@
       <c r="A7" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="40" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4412,15 +4421,15 @@
       <c r="A8" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="29" t="s">
+      <c r="B8" s="40" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="40" t="s">
         <v>268</v>
       </c>
     </row>
@@ -4428,7 +4437,7 @@
       <c r="A10" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="40" t="s">
         <v>269</v>
       </c>
     </row>
@@ -4436,7 +4445,7 @@
       <c r="A11" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="40" t="s">
         <v>270</v>
       </c>
     </row>
@@ -4444,15 +4453,15 @@
       <c r="A12" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="40" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="40" t="s">
         <v>271</v>
       </c>
     </row>
@@ -4460,7 +4469,7 @@
       <c r="A14" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="40" t="s">
         <v>272</v>
       </c>
     </row>
@@ -4468,7 +4477,7 @@
       <c r="A15" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B15" s="29" t="s">
+      <c r="B15" s="40" t="s">
         <v>273</v>
       </c>
     </row>
@@ -4476,7 +4485,7 @@
       <c r="A16" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="B16" s="29" t="s">
+      <c r="B16" s="40" t="s">
         <v>274</v>
       </c>
     </row>
@@ -4484,7 +4493,7 @@
       <c r="A17" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="40" t="s">
         <v>276</v>
       </c>
     </row>
@@ -4492,7 +4501,7 @@
       <c r="A18" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B18" s="40" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4500,7 +4509,7 @@
       <c r="A19" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B19" s="29" t="s">
+      <c r="B19" s="40" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4508,7 +4517,7 @@
       <c r="A20" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="40" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4516,7 +4525,7 @@
       <c r="A21" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="B21" s="29" t="s">
+      <c r="B21" s="40" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4524,7 +4533,7 @@
       <c r="A22" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="B22" s="29" t="s">
+      <c r="B22" s="40" t="s">
         <v>239</v>
       </c>
     </row>
@@ -4532,15 +4541,15 @@
       <c r="A23" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B23" s="29" t="s">
+      <c r="B23" s="40" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="40" t="s">
         <v>275</v>
       </c>
     </row>
@@ -4747,10 +4756,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="39" t="s">
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38" t="s">
         <v>222</v>
       </c>
     </row>
@@ -4762,7 +4771,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
         <v>288</v>
       </c>
@@ -4770,7 +4779,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
         <v>290</v>
       </c>
@@ -4835,7 +4844,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="10"/>

--- a/Material/2. Interviews & Surveys/Attribute Definition.xlsx
+++ b/Material/2. Interviews & Surveys/Attribute Definition.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\DSE_thesis\Material\2. Interviews &amp; Surveys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{903896E5-AFB6-4679-AD4A-63AC3B88E702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A69E113-5870-4011-8BD6-ACF6B1C24C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="824" activeTab="2" xr2:uid="{1010D4BD-99A2-4997-AD21-2857331DB82F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="824" xr2:uid="{1010D4BD-99A2-4997-AD21-2857331DB82F}"/>
   </bookViews>
   <sheets>
     <sheet name="Improvement" sheetId="9" r:id="rId1"/>
@@ -628,9 +628,6 @@
     <t>Attributes after Interviews</t>
   </si>
   <si>
-    <t>Attributes after Explanatory Survey + Text Analysis</t>
-  </si>
-  <si>
     <t>Personal Observation</t>
   </si>
   <si>
@@ -986,6 +983,9 @@
   </si>
   <si>
     <t>Introduced as a new attribute, mentioned in both interviews and the text analysis, reflecting a preference for less crowded areas.</t>
+  </si>
+  <si>
+    <t>Final Set of Attributes</t>
   </si>
 </sst>
 </file>
@@ -1608,7 +1608,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1735,6 +1735,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2135,14 +2141,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="44" t="s">
         <v>180</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="E1" s="19" t="s">
-        <v>190</v>
+      <c r="E1" s="44" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -2208,10 +2214,10 @@
         <v>142</v>
       </c>
       <c r="E7" s="36" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -4250,7 +4256,7 @@
         <v>104</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -4258,7 +4264,7 @@
         <v>103</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
@@ -4266,7 +4272,7 @@
         <v>142</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -4282,7 +4288,7 @@
         <v>169</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4306,7 +4312,7 @@
         <v>173</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -4366,7 +4372,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="41" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -4374,7 +4380,7 @@
         <v>145</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -4382,7 +4388,7 @@
         <v>146</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -4390,7 +4396,7 @@
         <v>147</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -4398,7 +4404,7 @@
         <v>148</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -4406,7 +4412,7 @@
         <v>149</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -4414,7 +4420,7 @@
         <v>150</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -4422,7 +4428,7 @@
         <v>151</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -4430,7 +4436,7 @@
         <v>152</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -4438,7 +4444,7 @@
         <v>153</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -4446,7 +4452,7 @@
         <v>154</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -4454,7 +4460,7 @@
         <v>155</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
@@ -4462,7 +4468,7 @@
         <v>156</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -4470,7 +4476,7 @@
         <v>157</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
@@ -4478,7 +4484,7 @@
         <v>158</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
@@ -4486,7 +4492,7 @@
         <v>159</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
@@ -4494,7 +4500,7 @@
         <v>160</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
@@ -4502,7 +4508,7 @@
         <v>161</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -4510,7 +4516,7 @@
         <v>162</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
@@ -4518,7 +4524,7 @@
         <v>163</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
@@ -4526,7 +4532,7 @@
         <v>164</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -4534,7 +4540,7 @@
         <v>165</v>
       </c>
       <c r="B22" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -4542,7 +4548,7 @@
         <v>166</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
@@ -4550,7 +4556,7 @@
         <v>167</v>
       </c>
       <c r="B24" s="40" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
   </sheetData>
@@ -4572,169 +4578,169 @@
         <v>0</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="B3" s="29" t="s">
         <v>238</v>
-      </c>
-      <c r="B3" s="29" t="s">
-        <v>239</v>
       </c>
       <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="22" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B4" s="29" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="22" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="22" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="22" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="22" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B8" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="22" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B9" s="29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="B10" s="29" t="s">
         <v>248</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="22" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B11" s="29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>251</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="B13" s="29" t="s">
         <v>253</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="29" t="s">
         <v>255</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="22" t="s">
+        <v>256</v>
+      </c>
+      <c r="B15" s="29" t="s">
         <v>257</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="B16" s="29" t="s">
         <v>259</v>
-      </c>
-      <c r="B16" s="29" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="22" t="s">
+        <v>260</v>
+      </c>
+      <c r="B17" s="29" t="s">
         <v>261</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="B19" s="29" t="s">
         <v>266</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="B20" s="29" t="s">
         <v>264</v>
-      </c>
-      <c r="B20" s="29" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="B21" s="29" t="s">
         <v>282</v>
-      </c>
-      <c r="B21" s="29" t="s">
-        <v>283</v>
       </c>
     </row>
   </sheetData>
@@ -4759,72 +4765,72 @@
       <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="38" t="s">
-        <v>222</v>
+      <c r="B1" s="43" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="36" t="s">
+        <v>285</v>
+      </c>
+      <c r="B2" s="8" t="s">
         <v>286</v>
       </c>
-      <c r="B2" s="8" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="36" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="B3" s="8" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="36" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="B4" s="8" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="36" t="s">
         <v>291</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="B5" s="8" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="36" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="B6" s="8" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="36" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="B7" s="8" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="36" t="s">
         <v>297</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>298</v>
       </c>
-      <c r="B8" s="8" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" s="36" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>300</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -4929,7 +4935,7 @@
         <v>108</v>
       </c>
       <c r="C1" s="24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
@@ -4940,7 +4946,7 @@
         <v>110</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -4960,7 +4966,7 @@
         <v>114</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -4980,7 +4986,7 @@
         <v>116</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -5000,7 +5006,7 @@
         <v>120</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -5011,7 +5017,7 @@
         <v>122</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
@@ -5022,7 +5028,7 @@
         <v>124</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -5033,7 +5039,7 @@
         <v>126</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -5044,7 +5050,7 @@
         <v>127</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -5064,7 +5070,7 @@
         <v>131</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -5084,7 +5090,7 @@
         <v>135</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
@@ -5104,7 +5110,7 @@
         <v>139</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -5115,7 +5121,7 @@
         <v>141</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -5392,7 +5398,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -5408,7 +5414,7 @@
         <v>9</v>
       </c>
       <c r="D2" s="33" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
@@ -5425,7 +5431,7 @@
         <v>9</v>
       </c>
       <c r="D3" s="33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -5442,7 +5448,7 @@
         <v>9</v>
       </c>
       <c r="D4" s="33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -5459,7 +5465,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -5476,7 +5482,7 @@
         <v>7</v>
       </c>
       <c r="D6" s="33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -5493,7 +5499,7 @@
         <v>7</v>
       </c>
       <c r="D7" s="33" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -5510,7 +5516,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -5527,7 +5533,7 @@
         <v>6</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -5544,7 +5550,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -5578,7 +5584,7 @@
         <v>5</v>
       </c>
       <c r="D12" s="33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -5595,7 +5601,7 @@
         <v>5</v>
       </c>
       <c r="D13" s="33" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -5612,7 +5618,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="33" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -5629,7 +5635,7 @@
         <v>5</v>
       </c>
       <c r="D15" s="33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -5646,7 +5652,7 @@
         <v>5</v>
       </c>
       <c r="D16" s="33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -5663,7 +5669,7 @@
         <v>4</v>
       </c>
       <c r="D17" s="33" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -5680,7 +5686,7 @@
         <v>4</v>
       </c>
       <c r="D18" s="33" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -5697,7 +5703,7 @@
         <v>4</v>
       </c>
       <c r="D19" s="33" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -5714,7 +5720,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -5731,7 +5737,7 @@
         <v>3</v>
       </c>
       <c r="D21" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -5748,7 +5754,7 @@
         <v>3</v>
       </c>
       <c r="D22" s="33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -5765,7 +5771,7 @@
         <v>3</v>
       </c>
       <c r="D23" s="33" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -5782,7 +5788,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -5799,7 +5805,7 @@
         <v>3</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -5816,7 +5822,7 @@
         <v>2</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -5833,7 +5839,7 @@
         <v>2</v>
       </c>
       <c r="D27" s="33" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -5850,7 +5856,7 @@
         <v>2</v>
       </c>
       <c r="D28" s="33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -5867,7 +5873,7 @@
         <v>2</v>
       </c>
       <c r="D29" s="33" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -5884,7 +5890,7 @@
         <v>2</v>
       </c>
       <c r="D30" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -5901,7 +5907,7 @@
         <v>2</v>
       </c>
       <c r="D31" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -5918,7 +5924,7 @@
         <v>2</v>
       </c>
       <c r="D32" s="33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -5935,7 +5941,7 @@
         <v>2</v>
       </c>
       <c r="D33" s="33" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -5952,7 +5958,7 @@
         <v>1</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -5969,7 +5975,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="33" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -5986,7 +5992,7 @@
         <v>1</v>
       </c>
       <c r="D36" s="33" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -6003,7 +6009,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="33" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -6020,7 +6026,7 @@
         <v>1</v>
       </c>
       <c r="D38" s="33" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -6037,7 +6043,7 @@
         <v>1</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -6054,7 +6060,7 @@
         <v>1</v>
       </c>
       <c r="D40" s="33" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -6071,7 +6077,7 @@
         <v>1</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -6088,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">

--- a/Material/2. Interviews & Surveys/Attribute Definition.xlsx
+++ b/Material/2. Interviews & Surveys/Attribute Definition.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\Documents\GitHub\DSE_thesis\Material\2. Interviews &amp; Surveys\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A69E113-5870-4011-8BD6-ACF6B1C24C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAECA4F-5D3C-47A3-BF52-4BAD8FF945AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="824" xr2:uid="{1010D4BD-99A2-4997-AD21-2857331DB82F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Improvement" sheetId="9" r:id="rId1"/>
-    <sheet name="Final Attirbutes" sheetId="4" r:id="rId2"/>
-    <sheet name="Short Survey - ChatGPT" sheetId="10" r:id="rId3"/>
-    <sheet name="Short Survey - Analysis" sheetId="8" r:id="rId4"/>
-    <sheet name="Accommodation Reviews" sheetId="11" r:id="rId5"/>
-    <sheet name="Interview Attributes" sheetId="6" r:id="rId6"/>
-    <sheet name="ChatGPT Attributes Refined" sheetId="7" r:id="rId7"/>
-    <sheet name="ChatGPT Attributes" sheetId="5" r:id="rId8"/>
-    <sheet name="Attribute_Frequency_Table" sheetId="2" r:id="rId9"/>
-    <sheet name="Attributes_by_Interview" sheetId="3" r:id="rId10"/>
+    <sheet name="For presentation" sheetId="12" r:id="rId1"/>
+    <sheet name="Improvement" sheetId="9" r:id="rId2"/>
+    <sheet name="Final Attirbutes" sheetId="4" r:id="rId3"/>
+    <sheet name="Short Survey - ChatGPT" sheetId="10" r:id="rId4"/>
+    <sheet name="Short Survey - Analysis" sheetId="8" r:id="rId5"/>
+    <sheet name="Accommodation Reviews" sheetId="11" r:id="rId6"/>
+    <sheet name="Interview Attributes" sheetId="6" r:id="rId7"/>
+    <sheet name="ChatGPT Attributes Refined" sheetId="7" r:id="rId8"/>
+    <sheet name="ChatGPT Attributes" sheetId="5" r:id="rId9"/>
+    <sheet name="Attribute_Frequency_Table" sheetId="2" r:id="rId10"/>
+    <sheet name="Attributes_by_Interview" sheetId="3" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Attributes_by_Interview!$B$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">Attributes_by_Interview!$B$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="304">
   <si>
     <t>Attribute</t>
   </si>
@@ -986,6 +987,12 @@
   </si>
   <si>
     <t>Final Set of Attributes</t>
+  </si>
+  <si>
+    <t>Attributes</t>
+  </si>
+  <si>
+    <t>Density of attractions within walking distance</t>
   </si>
 </sst>
 </file>
@@ -2127,6 +2134,2826 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B2C5ACC-E9DF-4CDE-AA80-CE0DFAA989CF}">
+  <dimension ref="A1:A15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="39.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="44" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="36" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="36" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="36" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="36" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="36" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="36" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="36" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="36" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="36" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="36" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="36" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="36" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="36" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753A4EC4-A069-4538-AB5A-AA8E0DF18E9E}">
+  <dimension ref="A1:D45"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="58.88671875" style="7" customWidth="1"/>
+    <col min="3" max="3" width="11.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="116.109375" style="8" customWidth="1"/>
+    <col min="5" max="16384" width="11.5546875" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="30" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="32">
+        <v>1</v>
+      </c>
+      <c r="B2" s="32" t="str">
+        <f>+VLOOKUP($A2,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>accommodation type</v>
+      </c>
+      <c r="C2" s="32">
+        <f>+VLOOKUP($A2,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>9</v>
+      </c>
+      <c r="D2" s="33" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="32">
+        <f>+A2+1</f>
+        <v>2</v>
+      </c>
+      <c r="B3" s="32" t="str">
+        <f>+VLOOKUP($A3,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>online recommendations</v>
+      </c>
+      <c r="C3" s="32">
+        <f>+VLOOKUP($A3,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>9</v>
+      </c>
+      <c r="D3" s="33" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="32">
+        <f t="shared" ref="A4:A45" si="0">+A3+1</f>
+        <v>3</v>
+      </c>
+      <c r="B4" s="32" t="str">
+        <f>+VLOOKUP($A4,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>proximity to other destinations</v>
+      </c>
+      <c r="C4" s="32">
+        <f>+VLOOKUP($A4,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>9</v>
+      </c>
+      <c r="D4" s="33" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="32">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="32" t="str">
+        <f>+VLOOKUP($A5,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>local cuisine</v>
+      </c>
+      <c r="C5" s="32">
+        <f>+VLOOKUP($A5,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>8</v>
+      </c>
+      <c r="D5" s="33" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="32">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="32" t="str">
+        <f>+VLOOKUP($A6,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>accessibility to touristic points</v>
+      </c>
+      <c r="C6" s="32">
+        <f>+VLOOKUP($A6,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>7</v>
+      </c>
+      <c r="D6" s="33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="32">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="32" t="str">
+        <f>+VLOOKUP($A7,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>cost to reach</v>
+      </c>
+      <c r="C7" s="32">
+        <f>+VLOOKUP($A7,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>7</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="32">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="32" t="str">
+        <f>+VLOOKUP($A8,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>accommodation price</v>
+      </c>
+      <c r="C8" s="32">
+        <f>+VLOOKUP($A8,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>6</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="32">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="32" t="str">
+        <f>+VLOOKUP($A9,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>distance to reach</v>
+      </c>
+      <c r="C9" s="32">
+        <f>+VLOOKUP($A9,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>6</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="32">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="32" t="str">
+        <f>+VLOOKUP($A10,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>historical buildings</v>
+      </c>
+      <c r="C10" s="32">
+        <f>+VLOOKUP($A10,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>6</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="32">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="32" t="str">
+        <f>+VLOOKUP($A11,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>local events</v>
+      </c>
+      <c r="C11" s="32">
+        <f>+VLOOKUP($A11,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>6</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="32">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="32" t="str">
+        <f>+VLOOKUP($A12,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>accommodation services</v>
+      </c>
+      <c r="C12" s="32">
+        <f>+VLOOKUP($A12,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>5</v>
+      </c>
+      <c r="D12" s="33" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="32">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="B13" s="32" t="str">
+        <f>+VLOOKUP($A13,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>availability of transport to destination</v>
+      </c>
+      <c r="C13" s="32">
+        <f>+VLOOKUP($A13,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>5</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="32">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="B14" s="32" t="str">
+        <f>+VLOOKUP($A14,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>cultural immersion</v>
+      </c>
+      <c r="C14" s="32">
+        <f>+VLOOKUP($A14,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>5</v>
+      </c>
+      <c r="D14" s="33" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="32">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="B15" s="32" t="str">
+        <f>+VLOOKUP($A15,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>food’s price</v>
+      </c>
+      <c r="C15" s="32">
+        <f>+VLOOKUP($A15,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>5</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="32">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="B16" s="32" t="str">
+        <f>+VLOOKUP($A16,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>proximity to popular cities</v>
+      </c>
+      <c r="C16" s="32">
+        <f>+VLOOKUP($A16,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>5</v>
+      </c>
+      <c r="D16" s="33" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="32">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="B17" s="32" t="str">
+        <f>+VLOOKUP($A17,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>accommodation location</v>
+      </c>
+      <c r="C17" s="32">
+        <f>+VLOOKUP($A17,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="32">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="B18" s="32" t="str">
+        <f>+VLOOKUP($A18,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>historical places</v>
+      </c>
+      <c r="C18" s="32">
+        <f>+VLOOKUP($A18,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="D18" s="33" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="32">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="B19" s="32" t="str">
+        <f>+VLOOKUP($A19,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>local prices</v>
+      </c>
+      <c r="C19" s="32">
+        <f>+VLOOKUP($A19,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="32">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="B20" s="32" t="str">
+        <f>+VLOOKUP($A20,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>natural landscape</v>
+      </c>
+      <c r="C20" s="32">
+        <f>+VLOOKUP($A20,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>4</v>
+      </c>
+      <c r="D20" s="33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="32">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="B21" s="32" t="str">
+        <f>+VLOOKUP($A21,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>access to beaches</v>
+      </c>
+      <c r="C21" s="32">
+        <f>+VLOOKUP($A21,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>3</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="32">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="B22" s="32" t="str">
+        <f>+VLOOKUP($A22,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>information availability online</v>
+      </c>
+      <c r="C22" s="32">
+        <f>+VLOOKUP($A22,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>3</v>
+      </c>
+      <c r="D22" s="33" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="32">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="B23" s="32" t="str">
+        <f>+VLOOKUP($A23,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>museums</v>
+      </c>
+      <c r="C23" s="32">
+        <f>+VLOOKUP($A23,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>3</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="32">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="B24" s="32" t="str">
+        <f>+VLOOKUP($A24,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>overcrowded</v>
+      </c>
+      <c r="C24" s="32">
+        <f>+VLOOKUP($A24,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>3</v>
+      </c>
+      <c r="D24" s="33" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="32">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="B25" s="32" t="str">
+        <f>+VLOOKUP($A25,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>restaurants availability</v>
+      </c>
+      <c r="C25" s="32">
+        <f>+VLOOKUP($A25,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>3</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="32">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+      <c r="B26" s="32" t="str">
+        <f>+VLOOKUP($A26,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>accessible by public transport</v>
+      </c>
+      <c r="C26" s="32">
+        <f>+VLOOKUP($A26,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="32">
+        <f t="shared" si="0"/>
+        <v>26</v>
+      </c>
+      <c r="B27" s="32" t="str">
+        <f>+VLOOKUP($A27,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>accommodation quality</v>
+      </c>
+      <c r="C27" s="32">
+        <f>+VLOOKUP($A27,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="32">
+        <f t="shared" si="0"/>
+        <v>27</v>
+      </c>
+      <c r="B28" s="32" t="str">
+        <f>+VLOOKUP($A28,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>city’s accessibility</v>
+      </c>
+      <c r="C28" s="32">
+        <f>+VLOOKUP($A28,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D28" s="33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="32">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="B29" s="32" t="str">
+        <f>+VLOOKUP($A29,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>genuine online recommendations</v>
+      </c>
+      <c r="C29" s="32">
+        <f>+VLOOKUP($A29,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D29" s="33" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="32">
+        <f t="shared" si="0"/>
+        <v>29</v>
+      </c>
+      <c r="B30" s="32" t="str">
+        <f>+VLOOKUP($A30,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>hiking trails</v>
+      </c>
+      <c r="C30" s="32">
+        <f>+VLOOKUP($A30,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D30" s="33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A31" s="32">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="B31" s="32" t="str">
+        <f>+VLOOKUP($A31,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>local friendliness</v>
+      </c>
+      <c r="C31" s="32">
+        <f>+VLOOKUP($A31,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="32">
+        <f t="shared" si="0"/>
+        <v>31</v>
+      </c>
+      <c r="B32" s="32" t="str">
+        <f>+VLOOKUP($A32,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>popular city</v>
+      </c>
+      <c r="C32" s="32">
+        <f>+VLOOKUP($A32,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D32" s="33" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="32">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="B33" s="32" t="str">
+        <f>+VLOOKUP($A33,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>variety of hours for transportation</v>
+      </c>
+      <c r="C33" s="32">
+        <f>+VLOOKUP($A33,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A34" s="32">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="B34" s="32" t="str">
+        <f>+VLOOKUP($A34,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>access to mountains</v>
+      </c>
+      <c r="C34" s="32">
+        <f>+VLOOKUP($A34,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D34" s="33" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A35" s="32">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="B35" s="32" t="str">
+        <f>+VLOOKUP($A35,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>attraction availability</v>
+      </c>
+      <c r="C35" s="32">
+        <f>+VLOOKUP($A35,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A36" s="32">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="B36" s="32" t="str">
+        <f>+VLOOKUP($A36,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>availability of city tours</v>
+      </c>
+      <c r="C36" s="32">
+        <f>+VLOOKUP($A36,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D36" s="33" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A37" s="32">
+        <f t="shared" si="0"/>
+        <v>36</v>
+      </c>
+      <c r="B37" s="32" t="str">
+        <f>+VLOOKUP($A37,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>availability of travel agencies</v>
+      </c>
+      <c r="C37" s="32">
+        <f>+VLOOKUP($A37,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A38" s="32">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+      <c r="B38" s="32" t="str">
+        <f>+VLOOKUP($A38,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>car friendly</v>
+      </c>
+      <c r="C38" s="32">
+        <f>+VLOOKUP($A38,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D38" s="33" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A39" s="32">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="B39" s="32" t="str">
+        <f>+VLOOKUP($A39,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>destination size</v>
+      </c>
+      <c r="C39" s="32">
+        <f>+VLOOKUP($A39,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A40" s="32">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="B40" s="32" t="str">
+        <f>+VLOOKUP($A40,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>events price</v>
+      </c>
+      <c r="C40" s="32">
+        <f>+VLOOKUP($A40,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A41" s="32">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="B41" s="32" t="str">
+        <f>+VLOOKUP($A41,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>local experience</v>
+      </c>
+      <c r="C41" s="32">
+        <f>+VLOOKUP($A41,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A42" s="32">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+      <c r="B42" s="32" t="str">
+        <f>+VLOOKUP($A42,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>local restaurants</v>
+      </c>
+      <c r="C42" s="32">
+        <f>+VLOOKUP($A42,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D42" s="33" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A43" s="32">
+        <f t="shared" si="0"/>
+        <v>42</v>
+      </c>
+      <c r="B43" s="32" t="str">
+        <f>+VLOOKUP($A43,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>music events</v>
+      </c>
+      <c r="C43" s="32">
+        <f>+VLOOKUP($A43,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A44" s="32">
+        <f t="shared" si="0"/>
+        <v>43</v>
+      </c>
+      <c r="B44" s="32" t="str">
+        <f>+VLOOKUP($A44,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>music events cost</v>
+      </c>
+      <c r="C44" s="32">
+        <f>+VLOOKUP($A44,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D44" s="33" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A45" s="34">
+        <f t="shared" si="0"/>
+        <v>44</v>
+      </c>
+      <c r="B45" s="34" t="str">
+        <f>+VLOOKUP($A45,Attributes_by_Interview!$A:$C,2,0)</f>
+        <v>supermarket availability</v>
+      </c>
+      <c r="C45" s="34">
+        <f>+VLOOKUP($A45,Attributes_by_Interview!$A:$C,3,0)</f>
+        <v>1</v>
+      </c>
+      <c r="D45" s="35"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374489E4-D186-42D3-A4E8-3A21A6E3345B}">
+  <dimension ref="A1:M45"/>
+  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <f>+IF(COUNTIF($C$1:C1,C2)&gt;0,RANK(C2,$C$2:$C$45,0)+COUNTIF($C$1:C1,C2),RANK(C2,$C$2:$C$45,0))</f>
+        <v>20</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="3">
+        <f>+SUM(D2:M2)</f>
+        <v>3</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3">
+        <v>1</v>
+      </c>
+      <c r="G2" s="3">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>0</v>
+      </c>
+      <c r="K2" s="3">
+        <v>0</v>
+      </c>
+      <c r="L2" s="3">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <f>+IF(COUNTIF($C$1:C2,C3)&gt;0,RANK(C3,$C$2:$C$45,0)+COUNTIF($C$1:C2,C3),RANK(C3,$C$2:$C$45,0))</f>
+        <v>33</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="3">
+        <f t="shared" ref="C3:C45" si="0">+SUM(D3:M3)</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <f>+IF(COUNTIF($C$1:C3,C4)&gt;0,RANK(C4,$C$2:$C$45,0)+COUNTIF($C$1:C3,C4),RANK(C4,$C$2:$C$45,0))</f>
+        <v>5</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>1</v>
+      </c>
+      <c r="M4" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <f>+IF(COUNTIF($C$1:C4,C5)&gt;0,RANK(C5,$C$2:$C$45,0)+COUNTIF($C$1:C4,C5),RANK(C5,$C$2:$C$45,0))</f>
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="3">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
+      </c>
+      <c r="J5" s="3">
+        <v>0</v>
+      </c>
+      <c r="K5" s="3">
+        <v>1</v>
+      </c>
+      <c r="L5" s="3">
+        <v>0</v>
+      </c>
+      <c r="M5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <f>+IF(COUNTIF($C$1:C5,C6)&gt;0,RANK(C6,$C$2:$C$45,0)+COUNTIF($C$1:C5,C6),RANK(C6,$C$2:$C$45,0))</f>
+        <v>16</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3">
+        <v>0</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>1</v>
+      </c>
+      <c r="M6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
+        <f>+IF(COUNTIF($C$1:C6,C7)&gt;0,RANK(C7,$C$2:$C$45,0)+COUNTIF($C$1:C6,C7),RANK(C7,$C$2:$C$45,0))</f>
+        <v>7</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
+        <f>+IF(COUNTIF($C$1:C7,C8)&gt;0,RANK(C8,$C$2:$C$45,0)+COUNTIF($C$1:C7,C8),RANK(C8,$C$2:$C$45,0))</f>
+        <v>26</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3">
+        <v>1</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
+        <f>+IF(COUNTIF($C$1:C8,C9)&gt;0,RANK(C9,$C$2:$C$45,0)+COUNTIF($C$1:C8,C9),RANK(C9,$C$2:$C$45,0))</f>
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
+        <f>+IF(COUNTIF($C$1:C9,C10)&gt;0,RANK(C10,$C$2:$C$45,0)+COUNTIF($C$1:C9,C10),RANK(C10,$C$2:$C$45,0))</f>
+        <v>1</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1</v>
+      </c>
+      <c r="K10" s="3">
+        <v>1</v>
+      </c>
+      <c r="L10" s="3">
+        <v>1</v>
+      </c>
+      <c r="M10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
+        <f>+IF(COUNTIF($C$1:C10,C11)&gt;0,RANK(C11,$C$2:$C$45,0)+COUNTIF($C$1:C10,C11),RANK(C11,$C$2:$C$45,0))</f>
+        <v>34</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>0</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
+        <f>+IF(COUNTIF($C$1:C11,C12)&gt;0,RANK(C12,$C$2:$C$45,0)+COUNTIF($C$1:C11,C12),RANK(C12,$C$2:$C$45,0))</f>
+        <v>35</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3">
+        <v>0</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>1</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
+        <f>+IF(COUNTIF($C$1:C12,C13)&gt;0,RANK(C13,$C$2:$C$45,0)+COUNTIF($C$1:C12,C13),RANK(C13,$C$2:$C$45,0))</f>
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
+      <c r="J13" s="3">
+        <v>1</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>1</v>
+      </c>
+      <c r="M13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
+        <f>+IF(COUNTIF($C$1:C13,C14)&gt;0,RANK(C14,$C$2:$C$45,0)+COUNTIF($C$1:C13,C14),RANK(C14,$C$2:$C$45,0))</f>
+        <v>36</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="3">
+        <f>+IF(COUNTIF($C$1:C14,C15)&gt;0,RANK(C15,$C$2:$C$45,0)+COUNTIF($C$1:C14,C15),RANK(C15,$C$2:$C$45,0))</f>
+        <v>37</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="3">
+        <f>+IF(COUNTIF($C$1:C15,C16)&gt;0,RANK(C16,$C$2:$C$45,0)+COUNTIF($C$1:C15,C16),RANK(C16,$C$2:$C$45,0))</f>
+        <v>27</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D16" s="3">
+        <v>0</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0</v>
+      </c>
+      <c r="F16" s="3">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <v>0</v>
+      </c>
+      <c r="I16" s="3">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3">
+        <v>1</v>
+      </c>
+      <c r="K16" s="3">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3">
+        <v>1</v>
+      </c>
+      <c r="M16" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A17" s="3">
+        <f>+IF(COUNTIF($C$1:C16,C17)&gt;0,RANK(C17,$C$2:$C$45,0)+COUNTIF($C$1:C16,C17),RANK(C17,$C$2:$C$45,0))</f>
+        <v>6</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1</v>
+      </c>
+      <c r="K17" s="3">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A18" s="3">
+        <f>+IF(COUNTIF($C$1:C17,C18)&gt;0,RANK(C18,$C$2:$C$45,0)+COUNTIF($C$1:C17,C18),RANK(C18,$C$2:$C$45,0))</f>
+        <v>13</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>0</v>
+      </c>
+      <c r="I18" s="3">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1</v>
+      </c>
+      <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A19" s="3">
+        <f>+IF(COUNTIF($C$1:C18,C19)&gt;0,RANK(C19,$C$2:$C$45,0)+COUNTIF($C$1:C18,C19),RANK(C19,$C$2:$C$45,0))</f>
+        <v>38</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D19" s="3">
+        <v>1</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>0</v>
+      </c>
+      <c r="G19" s="3">
+        <v>0</v>
+      </c>
+      <c r="H19" s="3">
+        <v>0</v>
+      </c>
+      <c r="I19" s="3">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3">
+        <v>0</v>
+      </c>
+      <c r="M19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A20" s="3">
+        <f>+IF(COUNTIF($C$1:C19,C20)&gt;0,RANK(C20,$C$2:$C$45,0)+COUNTIF($C$1:C19,C20),RANK(C20,$C$2:$C$45,0))</f>
+        <v>8</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D20" s="3">
+        <v>1</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
+        <v>1</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1</v>
+      </c>
+      <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>1</v>
+      </c>
+      <c r="J20" s="3">
+        <v>1</v>
+      </c>
+      <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
+        <v>1</v>
+      </c>
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A21" s="3">
+        <f>+IF(COUNTIF($C$1:C20,C21)&gt;0,RANK(C21,$C$2:$C$45,0)+COUNTIF($C$1:C20,C21),RANK(C21,$C$2:$C$45,0))</f>
+        <v>39</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C21" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
+        <v>0</v>
+      </c>
+      <c r="G21" s="3">
+        <v>0</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>1</v>
+      </c>
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A22" s="3">
+        <f>+IF(COUNTIF($C$1:C21,C22)&gt;0,RANK(C22,$C$2:$C$45,0)+COUNTIF($C$1:C21,C22),RANK(C22,$C$2:$C$45,0))</f>
+        <v>14</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D22" s="3">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>1</v>
+      </c>
+      <c r="J22" s="3">
+        <v>1</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A23" s="3">
+        <f>+IF(COUNTIF($C$1:C22,C23)&gt;0,RANK(C23,$C$2:$C$45,0)+COUNTIF($C$1:C22,C23),RANK(C23,$C$2:$C$45,0))</f>
+        <v>28</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D23" s="3">
+        <v>1</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+      <c r="F23" s="3">
+        <v>0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
+        <v>1</v>
+      </c>
+      <c r="M23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A24" s="3">
+        <f>+IF(COUNTIF($C$1:C23,C24)&gt;0,RANK(C24,$C$2:$C$45,0)+COUNTIF($C$1:C23,C24),RANK(C24,$C$2:$C$45,0))</f>
+        <v>29</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D24" s="3">
+        <v>1</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3">
+        <v>0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1</v>
+      </c>
+      <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A25" s="3">
+        <f>+IF(COUNTIF($C$1:C24,C25)&gt;0,RANK(C25,$C$2:$C$45,0)+COUNTIF($C$1:C24,C25),RANK(C25,$C$2:$C$45,0))</f>
+        <v>9</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1</v>
+      </c>
+      <c r="E25" s="3">
+        <v>1</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>1</v>
+      </c>
+      <c r="I25" s="3">
+        <v>1</v>
+      </c>
+      <c r="J25" s="3">
+        <v>1</v>
+      </c>
+      <c r="K25" s="3">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A26" s="3">
+        <f>+IF(COUNTIF($C$1:C25,C26)&gt;0,RANK(C26,$C$2:$C$45,0)+COUNTIF($C$1:C25,C26),RANK(C26,$C$2:$C$45,0))</f>
+        <v>17</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>0</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1</v>
+      </c>
+      <c r="J26" s="3">
+        <v>1</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>1</v>
+      </c>
+      <c r="M26" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A27" s="3">
+        <f>+IF(COUNTIF($C$1:C26,C27)&gt;0,RANK(C27,$C$2:$C$45,0)+COUNTIF($C$1:C26,C27),RANK(C27,$C$2:$C$45,0))</f>
+        <v>21</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D27" s="3">
+        <v>1</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1</v>
+      </c>
+      <c r="F27" s="3">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>0</v>
+      </c>
+      <c r="I27" s="3">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
+        <v>1</v>
+      </c>
+      <c r="M27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A28" s="3">
+        <f>+IF(COUNTIF($C$1:C27,C28)&gt;0,RANK(C28,$C$2:$C$45,0)+COUNTIF($C$1:C27,C28),RANK(C28,$C$2:$C$45,0))</f>
+        <v>4</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="3">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="D28" s="3">
+        <v>1</v>
+      </c>
+      <c r="E28" s="3">
+        <v>1</v>
+      </c>
+      <c r="F28" s="3">
+        <v>1</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>1</v>
+      </c>
+      <c r="I28" s="3">
+        <v>0</v>
+      </c>
+      <c r="J28" s="3">
+        <v>1</v>
+      </c>
+      <c r="K28" s="3">
+        <v>1</v>
+      </c>
+      <c r="L28" s="3">
+        <v>1</v>
+      </c>
+      <c r="M28" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A29" s="3">
+        <f>+IF(COUNTIF($C$1:C28,C29)&gt;0,RANK(C29,$C$2:$C$45,0)+COUNTIF($C$1:C28,C29),RANK(C29,$C$2:$C$45,0))</f>
+        <v>10</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="3">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>1</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1</v>
+      </c>
+      <c r="H29" s="3">
+        <v>1</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>1</v>
+      </c>
+      <c r="K29" s="3">
+        <v>1</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A30" s="3">
+        <f>+IF(COUNTIF($C$1:C29,C30)&gt;0,RANK(C30,$C$2:$C$45,0)+COUNTIF($C$1:C29,C30),RANK(C30,$C$2:$C$45,0))</f>
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3">
+        <v>1</v>
+      </c>
+      <c r="F30" s="3">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3">
+        <v>0</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0</v>
+      </c>
+      <c r="I30" s="3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A31" s="3">
+        <f>+IF(COUNTIF($C$1:C30,C31)&gt;0,RANK(C31,$C$2:$C$45,0)+COUNTIF($C$1:C30,C31),RANK(C31,$C$2:$C$45,0))</f>
+        <v>30</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0</v>
+      </c>
+      <c r="F31" s="3">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3">
+        <v>0</v>
+      </c>
+      <c r="H31" s="3">
+        <v>0</v>
+      </c>
+      <c r="I31" s="3">
+        <v>0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>1</v>
+      </c>
+      <c r="K31" s="3">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A32" s="3">
+        <f>+IF(COUNTIF($C$1:C31,C32)&gt;0,RANK(C32,$C$2:$C$45,0)+COUNTIF($C$1:C31,C32),RANK(C32,$C$2:$C$45,0))</f>
+        <v>18</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D32" s="3">
+        <v>1</v>
+      </c>
+      <c r="E32" s="3">
+        <v>1</v>
+      </c>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3">
+        <v>1</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A33" s="3">
+        <f>+IF(COUNTIF($C$1:C32,C33)&gt;0,RANK(C33,$C$2:$C$45,0)+COUNTIF($C$1:C32,C33),RANK(C33,$C$2:$C$45,0))</f>
+        <v>41</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+      <c r="F33" s="3">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0</v>
+      </c>
+      <c r="J33" s="3">
+        <v>1</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A34" s="3">
+        <f>+IF(COUNTIF($C$1:C33,C34)&gt;0,RANK(C34,$C$2:$C$45,0)+COUNTIF($C$1:C33,C34),RANK(C34,$C$2:$C$45,0))</f>
+        <v>22</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+      <c r="F34" s="3">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0</v>
+      </c>
+      <c r="J34" s="3">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3">
+        <v>1</v>
+      </c>
+      <c r="L34" s="3">
+        <v>1</v>
+      </c>
+      <c r="M34" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A35" s="3">
+        <f>+IF(COUNTIF($C$1:C34,C35)&gt;0,RANK(C35,$C$2:$C$45,0)+COUNTIF($C$1:C34,C35),RANK(C35,$C$2:$C$45,0))</f>
+        <v>42</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C35" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3">
+        <v>1</v>
+      </c>
+      <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A36" s="3">
+        <f>+IF(COUNTIF($C$1:C35,C36)&gt;0,RANK(C36,$C$2:$C$45,0)+COUNTIF($C$1:C35,C36),RANK(C36,$C$2:$C$45,0))</f>
+        <v>43</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C36" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0</v>
+      </c>
+      <c r="F36" s="3">
+        <v>0</v>
+      </c>
+      <c r="G36" s="3">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3">
+        <v>0</v>
+      </c>
+      <c r="I36" s="3">
+        <v>0</v>
+      </c>
+      <c r="J36" s="3">
+        <v>0</v>
+      </c>
+      <c r="K36" s="3">
+        <v>1</v>
+      </c>
+      <c r="L36" s="3">
+        <v>0</v>
+      </c>
+      <c r="M36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A37" s="3">
+        <f>+IF(COUNTIF($C$1:C36,C37)&gt;0,RANK(C37,$C$2:$C$45,0)+COUNTIF($C$1:C36,C37),RANK(C37,$C$2:$C$45,0))</f>
+        <v>19</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="3">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="D37" s="3">
+        <v>1</v>
+      </c>
+      <c r="E37" s="3">
+        <v>1</v>
+      </c>
+      <c r="F37" s="3">
+        <v>1</v>
+      </c>
+      <c r="G37" s="3">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3">
+        <v>0</v>
+      </c>
+      <c r="I37" s="3">
+        <v>0</v>
+      </c>
+      <c r="J37" s="3">
+        <v>0</v>
+      </c>
+      <c r="K37" s="3">
+        <v>0</v>
+      </c>
+      <c r="L37" s="3">
+        <v>0</v>
+      </c>
+      <c r="M37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A38" s="3">
+        <f>+IF(COUNTIF($C$1:C37,C38)&gt;0,RANK(C38,$C$2:$C$45,0)+COUNTIF($C$1:C37,C38),RANK(C38,$C$2:$C$45,0))</f>
+        <v>2</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="D38" s="3">
+        <v>1</v>
+      </c>
+      <c r="E38" s="3">
+        <v>1</v>
+      </c>
+      <c r="F38" s="3">
+        <v>1</v>
+      </c>
+      <c r="G38" s="3">
+        <v>1</v>
+      </c>
+      <c r="H38" s="3">
+        <v>0</v>
+      </c>
+      <c r="I38" s="3">
+        <v>1</v>
+      </c>
+      <c r="J38" s="3">
+        <v>1</v>
+      </c>
+      <c r="K38" s="3">
+        <v>1</v>
+      </c>
+      <c r="L38" s="3">
+        <v>1</v>
+      </c>
+      <c r="M38" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A39" s="3">
+        <f>+IF(COUNTIF($C$1:C38,C39)&gt;0,RANK(C39,$C$2:$C$45,0)+COUNTIF($C$1:C38,C39),RANK(C39,$C$2:$C$45,0))</f>
+        <v>23</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C39" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D39" s="3">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3">
+        <v>0</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <v>1</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0</v>
+      </c>
+      <c r="J39" s="3">
+        <v>1</v>
+      </c>
+      <c r="K39" s="3">
+        <v>1</v>
+      </c>
+      <c r="L39" s="3">
+        <v>0</v>
+      </c>
+      <c r="M39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A40" s="3">
+        <f>+IF(COUNTIF($C$1:C39,C40)&gt;0,RANK(C40,$C$2:$C$45,0)+COUNTIF($C$1:C39,C40),RANK(C40,$C$2:$C$45,0))</f>
+        <v>31</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C40" s="3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0</v>
+      </c>
+      <c r="F40" s="3">
+        <v>0</v>
+      </c>
+      <c r="G40" s="3">
+        <v>0</v>
+      </c>
+      <c r="H40" s="3">
+        <v>0</v>
+      </c>
+      <c r="I40" s="3">
+        <v>0</v>
+      </c>
+      <c r="J40" s="3">
+        <v>0</v>
+      </c>
+      <c r="K40" s="3">
+        <v>0</v>
+      </c>
+      <c r="L40" s="3">
+        <v>1</v>
+      </c>
+      <c r="M40" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A41" s="3">
+        <f>+IF(COUNTIF($C$1:C40,C41)&gt;0,RANK(C41,$C$2:$C$45,0)+COUNTIF($C$1:C40,C41),RANK(C41,$C$2:$C$45,0))</f>
+        <v>3</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C41" s="3">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="D41" s="3">
+        <v>1</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1</v>
+      </c>
+      <c r="F41" s="3">
+        <v>1</v>
+      </c>
+      <c r="G41" s="3">
+        <v>1</v>
+      </c>
+      <c r="H41" s="3">
+        <v>1</v>
+      </c>
+      <c r="I41" s="3">
+        <v>1</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>1</v>
+      </c>
+      <c r="L41" s="3">
+        <v>1</v>
+      </c>
+      <c r="M41" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A42" s="3">
+        <f>+IF(COUNTIF($C$1:C41,C42)&gt;0,RANK(C42,$C$2:$C$45,0)+COUNTIF($C$1:C41,C42),RANK(C42,$C$2:$C$45,0))</f>
+        <v>15</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C42" s="3">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>1</v>
+      </c>
+      <c r="F42" s="3">
+        <v>1</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>1</v>
+      </c>
+      <c r="I42" s="3">
+        <v>1</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
+        <v>1</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A43" s="3">
+        <f>+IF(COUNTIF($C$1:C42,C43)&gt;0,RANK(C43,$C$2:$C$45,0)+COUNTIF($C$1:C42,C43),RANK(C43,$C$2:$C$45,0))</f>
+        <v>24</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" s="3">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3">
+        <v>1</v>
+      </c>
+      <c r="G43" s="3">
+        <v>1</v>
+      </c>
+      <c r="H43" s="3">
+        <v>0</v>
+      </c>
+      <c r="I43" s="3">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3">
+        <v>1</v>
+      </c>
+      <c r="K43" s="3">
+        <v>0</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A44" s="3">
+        <f>+IF(COUNTIF($C$1:C43,C44)&gt;0,RANK(C44,$C$2:$C$45,0)+COUNTIF($C$1:C43,C44),RANK(C44,$C$2:$C$45,0))</f>
+        <v>44</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="3">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3">
+        <v>1</v>
+      </c>
+      <c r="H44" s="3">
+        <v>0</v>
+      </c>
+      <c r="I44" s="3">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3">
+        <v>0</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A45" s="4">
+        <f>+IF(COUNTIF($C$1:C44,C45)&gt;0,RANK(C45,$C$2:$C$45,0)+COUNTIF($C$1:C44,C45),RANK(C45,$C$2:$C$45,0))</f>
+        <v>32</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C45" s="4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="D45" s="4">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4">
+        <v>0</v>
+      </c>
+      <c r="G45" s="4">
+        <v>0</v>
+      </c>
+      <c r="H45" s="4">
+        <v>0</v>
+      </c>
+      <c r="I45" s="4">
+        <v>0</v>
+      </c>
+      <c r="J45" s="4">
+        <v>0</v>
+      </c>
+      <c r="K45" s="4">
+        <v>0</v>
+      </c>
+      <c r="L45" s="4">
+        <v>1</v>
+      </c>
+      <c r="M45" s="4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="B1:M1" xr:uid="{374489E4-D186-42D3-A4E8-3A21A6E3345B}"/>
+  <conditionalFormatting sqref="D2:M45">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E932CECC-0ABF-4430-A80C-09D6A62C6AD3}">
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2265,1963 +5092,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{374489E4-D186-42D3-A4E8-3A21A6E3345B}">
-  <dimension ref="A1:M45"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.44140625" style="1" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <f>+IF(COUNTIF($C$1:C1,C2)&gt;0,RANK(C2,$C$2:$C$45,0)+COUNTIF($C$1:C1,C2),RANK(C2,$C$2:$C$45,0))</f>
-        <v>20</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="3">
-        <f>+SUM(D2:M2)</f>
-        <v>3</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>1</v>
-      </c>
-      <c r="F2" s="3">
-        <v>1</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3">
-        <v>0</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <f>+IF(COUNTIF($C$1:C2,C3)&gt;0,RANK(C3,$C$2:$C$45,0)+COUNTIF($C$1:C2,C3),RANK(C3,$C$2:$C$45,0))</f>
-        <v>33</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="3">
-        <f t="shared" ref="C3:C45" si="0">+SUM(D3:M3)</f>
-        <v>1</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>0</v>
-      </c>
-      <c r="M3" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
-        <f>+IF(COUNTIF($C$1:C3,C4)&gt;0,RANK(C4,$C$2:$C$45,0)+COUNTIF($C$1:C3,C4),RANK(C4,$C$2:$C$45,0))</f>
-        <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="D4" s="3">
-        <v>1</v>
-      </c>
-      <c r="E4" s="3">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3">
-        <v>1</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3">
-        <v>1</v>
-      </c>
-      <c r="K4" s="3">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3">
-        <v>1</v>
-      </c>
-      <c r="M4" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
-        <f>+IF(COUNTIF($C$1:C4,C5)&gt;0,RANK(C5,$C$2:$C$45,0)+COUNTIF($C$1:C4,C5),RANK(C5,$C$2:$C$45,0))</f>
-        <v>25</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D5" s="3">
-        <v>1</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3">
-        <v>1</v>
-      </c>
-      <c r="L5" s="3">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
-        <f>+IF(COUNTIF($C$1:C5,C6)&gt;0,RANK(C6,$C$2:$C$45,0)+COUNTIF($C$1:C5,C6),RANK(C6,$C$2:$C$45,0))</f>
-        <v>16</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D6" s="3">
-        <v>1</v>
-      </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3">
-        <v>1</v>
-      </c>
-      <c r="M6" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <f>+IF(COUNTIF($C$1:C6,C7)&gt;0,RANK(C7,$C$2:$C$45,0)+COUNTIF($C$1:C6,C7),RANK(C7,$C$2:$C$45,0))</f>
-        <v>7</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1</v>
-      </c>
-      <c r="J7" s="3">
-        <v>1</v>
-      </c>
-      <c r="K7" s="3">
-        <v>1</v>
-      </c>
-      <c r="L7" s="3">
-        <v>1</v>
-      </c>
-      <c r="M7" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
-        <f>+IF(COUNTIF($C$1:C7,C8)&gt;0,RANK(C8,$C$2:$C$45,0)+COUNTIF($C$1:C7,C8),RANK(C8,$C$2:$C$45,0))</f>
-        <v>26</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>1</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1</v>
-      </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
-        <f>+IF(COUNTIF($C$1:C8,C9)&gt;0,RANK(C9,$C$2:$C$45,0)+COUNTIF($C$1:C8,C9),RANK(C9,$C$2:$C$45,0))</f>
-        <v>11</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>1</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>1</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
-        <f>+IF(COUNTIF($C$1:C9,C10)&gt;0,RANK(C10,$C$2:$C$45,0)+COUNTIF($C$1:C9,C10),RANK(C10,$C$2:$C$45,0))</f>
-        <v>1</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>1</v>
-      </c>
-      <c r="F10" s="3">
-        <v>1</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>1</v>
-      </c>
-      <c r="J10" s="3">
-        <v>1</v>
-      </c>
-      <c r="K10" s="3">
-        <v>1</v>
-      </c>
-      <c r="L10" s="3">
-        <v>1</v>
-      </c>
-      <c r="M10" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
-        <f>+IF(COUNTIF($C$1:C10,C11)&gt;0,RANK(C11,$C$2:$C$45,0)+COUNTIF($C$1:C10,C11),RANK(C11,$C$2:$C$45,0))</f>
-        <v>34</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0</v>
-      </c>
-      <c r="H11" s="3">
-        <v>1</v>
-      </c>
-      <c r="I11" s="3">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0</v>
-      </c>
-      <c r="L11" s="3">
-        <v>0</v>
-      </c>
-      <c r="M11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
-        <f>+IF(COUNTIF($C$1:C11,C12)&gt;0,RANK(C12,$C$2:$C$45,0)+COUNTIF($C$1:C11,C12),RANK(C12,$C$2:$C$45,0))</f>
-        <v>35</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3">
-        <v>0</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0</v>
-      </c>
-      <c r="I12" s="3">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3">
-        <v>0</v>
-      </c>
-      <c r="K12" s="3">
-        <v>0</v>
-      </c>
-      <c r="L12" s="3">
-        <v>1</v>
-      </c>
-      <c r="M12" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
-        <f>+IF(COUNTIF($C$1:C12,C13)&gt;0,RANK(C13,$C$2:$C$45,0)+COUNTIF($C$1:C12,C13),RANK(C13,$C$2:$C$45,0))</f>
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0</v>
-      </c>
-      <c r="H13" s="3">
-        <v>1</v>
-      </c>
-      <c r="I13" s="3">
-        <v>1</v>
-      </c>
-      <c r="J13" s="3">
-        <v>1</v>
-      </c>
-      <c r="K13" s="3">
-        <v>0</v>
-      </c>
-      <c r="L13" s="3">
-        <v>1</v>
-      </c>
-      <c r="M13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
-        <f>+IF(COUNTIF($C$1:C13,C14)&gt;0,RANK(C14,$C$2:$C$45,0)+COUNTIF($C$1:C13,C14),RANK(C14,$C$2:$C$45,0))</f>
-        <v>36</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>1</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
-        <f>+IF(COUNTIF($C$1:C14,C15)&gt;0,RANK(C15,$C$2:$C$45,0)+COUNTIF($C$1:C14,C15),RANK(C15,$C$2:$C$45,0))</f>
-        <v>37</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D15" s="3">
-        <v>0</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>1</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
-        <f>+IF(COUNTIF($C$1:C15,C16)&gt;0,RANK(C16,$C$2:$C$45,0)+COUNTIF($C$1:C15,C16),RANK(C16,$C$2:$C$45,0))</f>
-        <v>27</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C16" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D16" s="3">
-        <v>0</v>
-      </c>
-      <c r="E16" s="3">
-        <v>0</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0</v>
-      </c>
-      <c r="G16" s="3">
-        <v>0</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0</v>
-      </c>
-      <c r="I16" s="3">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3">
-        <v>1</v>
-      </c>
-      <c r="K16" s="3">
-        <v>0</v>
-      </c>
-      <c r="L16" s="3">
-        <v>1</v>
-      </c>
-      <c r="M16" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
-        <f>+IF(COUNTIF($C$1:C16,C17)&gt;0,RANK(C17,$C$2:$C$45,0)+COUNTIF($C$1:C16,C17),RANK(C17,$C$2:$C$45,0))</f>
-        <v>6</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="3">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="D17" s="3">
-        <v>1</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3">
-        <v>1</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1</v>
-      </c>
-      <c r="I17" s="3">
-        <v>1</v>
-      </c>
-      <c r="J17" s="3">
-        <v>1</v>
-      </c>
-      <c r="K17" s="3">
-        <v>0</v>
-      </c>
-      <c r="L17" s="3">
-        <v>0</v>
-      </c>
-      <c r="M17" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
-        <f>+IF(COUNTIF($C$1:C17,C18)&gt;0,RANK(C18,$C$2:$C$45,0)+COUNTIF($C$1:C17,C18),RANK(C18,$C$2:$C$45,0))</f>
-        <v>13</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D18" s="3">
-        <v>1</v>
-      </c>
-      <c r="E18" s="3">
-        <v>1</v>
-      </c>
-      <c r="F18" s="3">
-        <v>1</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0</v>
-      </c>
-      <c r="I18" s="3">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
-        <v>1</v>
-      </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
-        <f>+IF(COUNTIF($C$1:C18,C19)&gt;0,RANK(C19,$C$2:$C$45,0)+COUNTIF($C$1:C18,C19),RANK(C19,$C$2:$C$45,0))</f>
-        <v>38</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D19" s="3">
-        <v>1</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0</v>
-      </c>
-      <c r="I19" s="3">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3">
-        <v>0</v>
-      </c>
-      <c r="K19" s="3">
-        <v>0</v>
-      </c>
-      <c r="L19" s="3">
-        <v>0</v>
-      </c>
-      <c r="M19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
-        <f>+IF(COUNTIF($C$1:C19,C20)&gt;0,RANK(C20,$C$2:$C$45,0)+COUNTIF($C$1:C19,C20),RANK(C20,$C$2:$C$45,0))</f>
-        <v>8</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D20" s="3">
-        <v>1</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>1</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>1</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1</v>
-      </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
-        <v>1</v>
-      </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
-        <f>+IF(COUNTIF($C$1:C20,C21)&gt;0,RANK(C21,$C$2:$C$45,0)+COUNTIF($C$1:C20,C21),RANK(C21,$C$2:$C$45,0))</f>
-        <v>39</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D21" s="3">
-        <v>0</v>
-      </c>
-      <c r="E21" s="3">
-        <v>0</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3">
-        <v>1</v>
-      </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
-        <f>+IF(COUNTIF($C$1:C21,C22)&gt;0,RANK(C22,$C$2:$C$45,0)+COUNTIF($C$1:C21,C22),RANK(C22,$C$2:$C$45,0))</f>
-        <v>14</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D22" s="3">
-        <v>1</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>1</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
-        <f>+IF(COUNTIF($C$1:C22,C23)&gt;0,RANK(C23,$C$2:$C$45,0)+COUNTIF($C$1:C22,C23),RANK(C23,$C$2:$C$45,0))</f>
-        <v>28</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C23" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D23" s="3">
-        <v>1</v>
-      </c>
-      <c r="E23" s="3">
-        <v>0</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0</v>
-      </c>
-      <c r="I23" s="3">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3">
-        <v>0</v>
-      </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
-      <c r="L23" s="3">
-        <v>1</v>
-      </c>
-      <c r="M23" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
-        <f>+IF(COUNTIF($C$1:C23,C24)&gt;0,RANK(C24,$C$2:$C$45,0)+COUNTIF($C$1:C23,C24),RANK(C24,$C$2:$C$45,0))</f>
-        <v>29</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D24" s="3">
-        <v>1</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
-        <f>+IF(COUNTIF($C$1:C24,C25)&gt;0,RANK(C25,$C$2:$C$45,0)+COUNTIF($C$1:C24,C25),RANK(C25,$C$2:$C$45,0))</f>
-        <v>9</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C25" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D25" s="3">
-        <v>1</v>
-      </c>
-      <c r="E25" s="3">
-        <v>1</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3">
-        <v>1</v>
-      </c>
-      <c r="I25" s="3">
-        <v>1</v>
-      </c>
-      <c r="J25" s="3">
-        <v>1</v>
-      </c>
-      <c r="K25" s="3">
-        <v>0</v>
-      </c>
-      <c r="L25" s="3">
-        <v>0</v>
-      </c>
-      <c r="M25" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
-        <f>+IF(COUNTIF($C$1:C25,C26)&gt;0,RANK(C26,$C$2:$C$45,0)+COUNTIF($C$1:C25,C26),RANK(C26,$C$2:$C$45,0))</f>
-        <v>17</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C26" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D26" s="3">
-        <v>0</v>
-      </c>
-      <c r="E26" s="3">
-        <v>0</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0</v>
-      </c>
-      <c r="H26" s="3">
-        <v>0</v>
-      </c>
-      <c r="I26" s="3">
-        <v>1</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1</v>
-      </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
-      <c r="L26" s="3">
-        <v>1</v>
-      </c>
-      <c r="M26" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
-        <f>+IF(COUNTIF($C$1:C26,C27)&gt;0,RANK(C27,$C$2:$C$45,0)+COUNTIF($C$1:C26,C27),RANK(C27,$C$2:$C$45,0))</f>
-        <v>21</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D27" s="3">
-        <v>1</v>
-      </c>
-      <c r="E27" s="3">
-        <v>1</v>
-      </c>
-      <c r="F27" s="3">
-        <v>0</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0</v>
-      </c>
-      <c r="I27" s="3">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
-      <c r="L27" s="3">
-        <v>1</v>
-      </c>
-      <c r="M27" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
-        <f>+IF(COUNTIF($C$1:C27,C28)&gt;0,RANK(C28,$C$2:$C$45,0)+COUNTIF($C$1:C27,C28),RANK(C28,$C$2:$C$45,0))</f>
-        <v>4</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="3">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="3">
-        <v>1</v>
-      </c>
-      <c r="F28" s="3">
-        <v>1</v>
-      </c>
-      <c r="G28" s="3">
-        <v>0</v>
-      </c>
-      <c r="H28" s="3">
-        <v>1</v>
-      </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3">
-        <v>1</v>
-      </c>
-      <c r="K28" s="3">
-        <v>1</v>
-      </c>
-      <c r="L28" s="3">
-        <v>1</v>
-      </c>
-      <c r="M28" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
-        <f>+IF(COUNTIF($C$1:C28,C29)&gt;0,RANK(C29,$C$2:$C$45,0)+COUNTIF($C$1:C28,C29),RANK(C29,$C$2:$C$45,0))</f>
-        <v>10</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="3">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="D29" s="3">
-        <v>1</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>1</v>
-      </c>
-      <c r="G29" s="3">
-        <v>1</v>
-      </c>
-      <c r="H29" s="3">
-        <v>1</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>1</v>
-      </c>
-      <c r="K29" s="3">
-        <v>1</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
-        <f>+IF(COUNTIF($C$1:C29,C30)&gt;0,RANK(C30,$C$2:$C$45,0)+COUNTIF($C$1:C29,C30),RANK(C30,$C$2:$C$45,0))</f>
-        <v>40</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C30" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D30" s="3">
-        <v>0</v>
-      </c>
-      <c r="E30" s="3">
-        <v>1</v>
-      </c>
-      <c r="F30" s="3">
-        <v>0</v>
-      </c>
-      <c r="G30" s="3">
-        <v>0</v>
-      </c>
-      <c r="H30" s="3">
-        <v>0</v>
-      </c>
-      <c r="I30" s="3">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3">
-        <v>0</v>
-      </c>
-      <c r="K30" s="3">
-        <v>0</v>
-      </c>
-      <c r="L30" s="3">
-        <v>0</v>
-      </c>
-      <c r="M30" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
-        <f>+IF(COUNTIF($C$1:C30,C31)&gt;0,RANK(C31,$C$2:$C$45,0)+COUNTIF($C$1:C30,C31),RANK(C31,$C$2:$C$45,0))</f>
-        <v>30</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D31" s="3">
-        <v>0</v>
-      </c>
-      <c r="E31" s="3">
-        <v>0</v>
-      </c>
-      <c r="F31" s="3">
-        <v>0</v>
-      </c>
-      <c r="G31" s="3">
-        <v>0</v>
-      </c>
-      <c r="H31" s="3">
-        <v>0</v>
-      </c>
-      <c r="I31" s="3">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3">
-        <v>1</v>
-      </c>
-      <c r="K31" s="3">
-        <v>0</v>
-      </c>
-      <c r="L31" s="3">
-        <v>0</v>
-      </c>
-      <c r="M31" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
-        <f>+IF(COUNTIF($C$1:C31,C32)&gt;0,RANK(C32,$C$2:$C$45,0)+COUNTIF($C$1:C31,C32),RANK(C32,$C$2:$C$45,0))</f>
-        <v>18</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D32" s="3">
-        <v>1</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
-      </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
-        <f>+IF(COUNTIF($C$1:C32,C33)&gt;0,RANK(C33,$C$2:$C$45,0)+COUNTIF($C$1:C32,C33),RANK(C33,$C$2:$C$45,0))</f>
-        <v>41</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D33" s="3">
-        <v>0</v>
-      </c>
-      <c r="E33" s="3">
-        <v>0</v>
-      </c>
-      <c r="F33" s="3">
-        <v>0</v>
-      </c>
-      <c r="G33" s="3">
-        <v>0</v>
-      </c>
-      <c r="H33" s="3">
-        <v>0</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1</v>
-      </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
-        <f>+IF(COUNTIF($C$1:C33,C34)&gt;0,RANK(C34,$C$2:$C$45,0)+COUNTIF($C$1:C33,C34),RANK(C34,$C$2:$C$45,0))</f>
-        <v>22</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C34" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D34" s="3">
-        <v>0</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0</v>
-      </c>
-      <c r="F34" s="3">
-        <v>0</v>
-      </c>
-      <c r="G34" s="3">
-        <v>0</v>
-      </c>
-      <c r="H34" s="3">
-        <v>0</v>
-      </c>
-      <c r="I34" s="3">
-        <v>0</v>
-      </c>
-      <c r="J34" s="3">
-        <v>0</v>
-      </c>
-      <c r="K34" s="3">
-        <v>1</v>
-      </c>
-      <c r="L34" s="3">
-        <v>1</v>
-      </c>
-      <c r="M34" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
-        <f>+IF(COUNTIF($C$1:C34,C35)&gt;0,RANK(C35,$C$2:$C$45,0)+COUNTIF($C$1:C34,C35),RANK(C35,$C$2:$C$45,0))</f>
-        <v>42</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D35" s="3">
-        <v>0</v>
-      </c>
-      <c r="E35" s="3">
-        <v>0</v>
-      </c>
-      <c r="F35" s="3">
-        <v>0</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0</v>
-      </c>
-      <c r="H35" s="3">
-        <v>0</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
-        <v>1</v>
-      </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
-        <f>+IF(COUNTIF($C$1:C35,C36)&gt;0,RANK(C36,$C$2:$C$45,0)+COUNTIF($C$1:C35,C36),RANK(C36,$C$2:$C$45,0))</f>
-        <v>43</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D36" s="3">
-        <v>0</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3">
-        <v>0</v>
-      </c>
-      <c r="G36" s="3">
-        <v>0</v>
-      </c>
-      <c r="H36" s="3">
-        <v>0</v>
-      </c>
-      <c r="I36" s="3">
-        <v>0</v>
-      </c>
-      <c r="J36" s="3">
-        <v>0</v>
-      </c>
-      <c r="K36" s="3">
-        <v>1</v>
-      </c>
-      <c r="L36" s="3">
-        <v>0</v>
-      </c>
-      <c r="M36" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="3">
-        <f>+IF(COUNTIF($C$1:C36,C37)&gt;0,RANK(C37,$C$2:$C$45,0)+COUNTIF($C$1:C36,C37),RANK(C37,$C$2:$C$45,0))</f>
-        <v>19</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C37" s="3">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="D37" s="3">
-        <v>1</v>
-      </c>
-      <c r="E37" s="3">
-        <v>1</v>
-      </c>
-      <c r="F37" s="3">
-        <v>1</v>
-      </c>
-      <c r="G37" s="3">
-        <v>1</v>
-      </c>
-      <c r="H37" s="3">
-        <v>0</v>
-      </c>
-      <c r="I37" s="3">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3">
-        <v>0</v>
-      </c>
-      <c r="K37" s="3">
-        <v>0</v>
-      </c>
-      <c r="L37" s="3">
-        <v>0</v>
-      </c>
-      <c r="M37" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="3">
-        <f>+IF(COUNTIF($C$1:C37,C38)&gt;0,RANK(C38,$C$2:$C$45,0)+COUNTIF($C$1:C37,C38),RANK(C38,$C$2:$C$45,0))</f>
-        <v>2</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C38" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="D38" s="3">
-        <v>1</v>
-      </c>
-      <c r="E38" s="3">
-        <v>1</v>
-      </c>
-      <c r="F38" s="3">
-        <v>1</v>
-      </c>
-      <c r="G38" s="3">
-        <v>1</v>
-      </c>
-      <c r="H38" s="3">
-        <v>0</v>
-      </c>
-      <c r="I38" s="3">
-        <v>1</v>
-      </c>
-      <c r="J38" s="3">
-        <v>1</v>
-      </c>
-      <c r="K38" s="3">
-        <v>1</v>
-      </c>
-      <c r="L38" s="3">
-        <v>1</v>
-      </c>
-      <c r="M38" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="3">
-        <f>+IF(COUNTIF($C$1:C38,C39)&gt;0,RANK(C39,$C$2:$C$45,0)+COUNTIF($C$1:C38,C39),RANK(C39,$C$2:$C$45,0))</f>
-        <v>23</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C39" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D39" s="3">
-        <v>0</v>
-      </c>
-      <c r="E39" s="3">
-        <v>0</v>
-      </c>
-      <c r="F39" s="3">
-        <v>0</v>
-      </c>
-      <c r="G39" s="3">
-        <v>0</v>
-      </c>
-      <c r="H39" s="3">
-        <v>1</v>
-      </c>
-      <c r="I39" s="3">
-        <v>0</v>
-      </c>
-      <c r="J39" s="3">
-        <v>1</v>
-      </c>
-      <c r="K39" s="3">
-        <v>1</v>
-      </c>
-      <c r="L39" s="3">
-        <v>0</v>
-      </c>
-      <c r="M39" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
-        <f>+IF(COUNTIF($C$1:C39,C40)&gt;0,RANK(C40,$C$2:$C$45,0)+COUNTIF($C$1:C39,C40),RANK(C40,$C$2:$C$45,0))</f>
-        <v>31</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C40" s="3">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D40" s="3">
-        <v>0</v>
-      </c>
-      <c r="E40" s="3">
-        <v>0</v>
-      </c>
-      <c r="F40" s="3">
-        <v>0</v>
-      </c>
-      <c r="G40" s="3">
-        <v>0</v>
-      </c>
-      <c r="H40" s="3">
-        <v>0</v>
-      </c>
-      <c r="I40" s="3">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3">
-        <v>0</v>
-      </c>
-      <c r="K40" s="3">
-        <v>0</v>
-      </c>
-      <c r="L40" s="3">
-        <v>1</v>
-      </c>
-      <c r="M40" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="3">
-        <f>+IF(COUNTIF($C$1:C40,C41)&gt;0,RANK(C41,$C$2:$C$45,0)+COUNTIF($C$1:C40,C41),RANK(C41,$C$2:$C$45,0))</f>
-        <v>3</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C41" s="3">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="D41" s="3">
-        <v>1</v>
-      </c>
-      <c r="E41" s="3">
-        <v>1</v>
-      </c>
-      <c r="F41" s="3">
-        <v>1</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1</v>
-      </c>
-      <c r="H41" s="3">
-        <v>1</v>
-      </c>
-      <c r="I41" s="3">
-        <v>1</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3">
-        <v>1</v>
-      </c>
-      <c r="L41" s="3">
-        <v>1</v>
-      </c>
-      <c r="M41" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
-        <f>+IF(COUNTIF($C$1:C41,C42)&gt;0,RANK(C42,$C$2:$C$45,0)+COUNTIF($C$1:C41,C42),RANK(C42,$C$2:$C$45,0))</f>
-        <v>15</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C42" s="3">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>1</v>
-      </c>
-      <c r="F42" s="3">
-        <v>1</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>1</v>
-      </c>
-      <c r="I42" s="3">
-        <v>1</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
-      <c r="L42" s="3">
-        <v>1</v>
-      </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
-        <f>+IF(COUNTIF($C$1:C42,C43)&gt;0,RANK(C43,$C$2:$C$45,0)+COUNTIF($C$1:C42,C43),RANK(C43,$C$2:$C$45,0))</f>
-        <v>24</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" s="3">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="D43" s="3">
-        <v>0</v>
-      </c>
-      <c r="E43" s="3">
-        <v>0</v>
-      </c>
-      <c r="F43" s="3">
-        <v>1</v>
-      </c>
-      <c r="G43" s="3">
-        <v>1</v>
-      </c>
-      <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>1</v>
-      </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="3">
-        <f>+IF(COUNTIF($C$1:C43,C44)&gt;0,RANK(C44,$C$2:$C$45,0)+COUNTIF($C$1:C43,C44),RANK(C44,$C$2:$C$45,0))</f>
-        <v>44</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C44" s="3">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>1</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="4">
-        <f>+IF(COUNTIF($C$1:C44,C45)&gt;0,RANK(C45,$C$2:$C$45,0)+COUNTIF($C$1:C44,C45),RANK(C45,$C$2:$C$45,0))</f>
-        <v>32</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45" s="4">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="D45" s="4">
-        <v>0</v>
-      </c>
-      <c r="E45" s="4">
-        <v>0</v>
-      </c>
-      <c r="F45" s="4">
-        <v>0</v>
-      </c>
-      <c r="G45" s="4">
-        <v>0</v>
-      </c>
-      <c r="H45" s="4">
-        <v>0</v>
-      </c>
-      <c r="I45" s="4">
-        <v>0</v>
-      </c>
-      <c r="J45" s="4">
-        <v>0</v>
-      </c>
-      <c r="K45" s="4">
-        <v>0</v>
-      </c>
-      <c r="L45" s="4">
-        <v>1</v>
-      </c>
-      <c r="M45" s="4">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="B1:M1" xr:uid="{374489E4-D186-42D3-A4E8-3A21A6E3345B}"/>
-  <conditionalFormatting sqref="D2:M45">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35B2167B-80CA-4E4B-99D3-44B58628E678}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -4358,7 +5229,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7D004CF-400B-48FE-A209-2ACF427E9E83}">
   <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4564,7 +5435,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23BBD249-A1E7-43DF-9246-67B68F7E61DE}">
   <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4748,7 +5619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3080E8F-053B-4DC2-938F-1F9C39658CB5}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -4838,7 +5709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D035974D-1E8B-4D6B-B792-45DE29931EED}">
   <sheetPr>
     <tabColor rgb="FF00B050"/>
@@ -4916,7 +5787,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC3E7FF2-47BB-4C40-BD9E-1B45503CF1C0}">
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5129,7 +6000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F69F90F1-9B4F-4DDC-ACBE-ED45C29C359A}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -5369,782 +6240,6 @@
       <c r="C21" s="18" t="s">
         <v>101</v>
       </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{753A4EC4-A069-4538-AB5A-AA8E0DF18E9E}">
-  <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="3" style="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58.88671875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="116.109375" style="8" customWidth="1"/>
-    <col min="5" max="16384" width="11.5546875" style="12"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="32">
-        <v>1</v>
-      </c>
-      <c r="B2" s="32" t="str">
-        <f>+VLOOKUP($A2,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>accommodation type</v>
-      </c>
-      <c r="C2" s="32">
-        <f>+VLOOKUP($A2,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>9</v>
-      </c>
-      <c r="D2" s="33" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="32">
-        <f>+A2+1</f>
-        <v>2</v>
-      </c>
-      <c r="B3" s="32" t="str">
-        <f>+VLOOKUP($A3,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>online recommendations</v>
-      </c>
-      <c r="C3" s="32">
-        <f>+VLOOKUP($A3,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>9</v>
-      </c>
-      <c r="D3" s="33" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="32">
-        <f t="shared" ref="A4:A45" si="0">+A3+1</f>
-        <v>3</v>
-      </c>
-      <c r="B4" s="32" t="str">
-        <f>+VLOOKUP($A4,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>proximity to other destinations</v>
-      </c>
-      <c r="C4" s="32">
-        <f>+VLOOKUP($A4,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>9</v>
-      </c>
-      <c r="D4" s="33" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="32">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B5" s="32" t="str">
-        <f>+VLOOKUP($A5,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>local cuisine</v>
-      </c>
-      <c r="C5" s="32">
-        <f>+VLOOKUP($A5,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>8</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="32">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B6" s="32" t="str">
-        <f>+VLOOKUP($A6,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>accessibility to touristic points</v>
-      </c>
-      <c r="C6" s="32">
-        <f>+VLOOKUP($A6,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>7</v>
-      </c>
-      <c r="D6" s="33" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="32">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B7" s="32" t="str">
-        <f>+VLOOKUP($A7,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>cost to reach</v>
-      </c>
-      <c r="C7" s="32">
-        <f>+VLOOKUP($A7,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>7</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="32">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8" s="32" t="str">
-        <f>+VLOOKUP($A8,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>accommodation price</v>
-      </c>
-      <c r="C8" s="32">
-        <f>+VLOOKUP($A8,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>6</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="32">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" s="32" t="str">
-        <f>+VLOOKUP($A9,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>distance to reach</v>
-      </c>
-      <c r="C9" s="32">
-        <f>+VLOOKUP($A9,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>6</v>
-      </c>
-      <c r="D9" s="33" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="32">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B10" s="32" t="str">
-        <f>+VLOOKUP($A10,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>historical buildings</v>
-      </c>
-      <c r="C10" s="32">
-        <f>+VLOOKUP($A10,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>6</v>
-      </c>
-      <c r="D10" s="33" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="32">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B11" s="32" t="str">
-        <f>+VLOOKUP($A11,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>local events</v>
-      </c>
-      <c r="C11" s="32">
-        <f>+VLOOKUP($A11,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>6</v>
-      </c>
-      <c r="D11" s="33" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="32">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" s="32" t="str">
-        <f>+VLOOKUP($A12,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>accommodation services</v>
-      </c>
-      <c r="C12" s="32">
-        <f>+VLOOKUP($A12,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>5</v>
-      </c>
-      <c r="D12" s="33" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="32">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13" s="32" t="str">
-        <f>+VLOOKUP($A13,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>availability of transport to destination</v>
-      </c>
-      <c r="C13" s="32">
-        <f>+VLOOKUP($A13,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>5</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="32">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14" s="32" t="str">
-        <f>+VLOOKUP($A14,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>cultural immersion</v>
-      </c>
-      <c r="C14" s="32">
-        <f>+VLOOKUP($A14,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>5</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="32">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" s="32" t="str">
-        <f>+VLOOKUP($A15,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>food’s price</v>
-      </c>
-      <c r="C15" s="32">
-        <f>+VLOOKUP($A15,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>5</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="32">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" s="32" t="str">
-        <f>+VLOOKUP($A16,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>proximity to popular cities</v>
-      </c>
-      <c r="C16" s="32">
-        <f>+VLOOKUP($A16,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>5</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="32">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B17" s="32" t="str">
-        <f>+VLOOKUP($A17,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>accommodation location</v>
-      </c>
-      <c r="C17" s="32">
-        <f>+VLOOKUP($A17,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>4</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="32">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B18" s="32" t="str">
-        <f>+VLOOKUP($A18,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>historical places</v>
-      </c>
-      <c r="C18" s="32">
-        <f>+VLOOKUP($A18,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>4</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="32">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B19" s="32" t="str">
-        <f>+VLOOKUP($A19,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>local prices</v>
-      </c>
-      <c r="C19" s="32">
-        <f>+VLOOKUP($A19,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>4</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="32">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B20" s="32" t="str">
-        <f>+VLOOKUP($A20,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>natural landscape</v>
-      </c>
-      <c r="C20" s="32">
-        <f>+VLOOKUP($A20,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>4</v>
-      </c>
-      <c r="D20" s="33" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="32">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B21" s="32" t="str">
-        <f>+VLOOKUP($A21,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>access to beaches</v>
-      </c>
-      <c r="C21" s="32">
-        <f>+VLOOKUP($A21,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>3</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="32">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B22" s="32" t="str">
-        <f>+VLOOKUP($A22,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>information availability online</v>
-      </c>
-      <c r="C22" s="32">
-        <f>+VLOOKUP($A22,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>3</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="32">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B23" s="32" t="str">
-        <f>+VLOOKUP($A23,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>museums</v>
-      </c>
-      <c r="C23" s="32">
-        <f>+VLOOKUP($A23,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>3</v>
-      </c>
-      <c r="D23" s="33" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="32">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B24" s="32" t="str">
-        <f>+VLOOKUP($A24,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>overcrowded</v>
-      </c>
-      <c r="C24" s="32">
-        <f>+VLOOKUP($A24,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>3</v>
-      </c>
-      <c r="D24" s="33" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="32">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B25" s="32" t="str">
-        <f>+VLOOKUP($A25,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>restaurants availability</v>
-      </c>
-      <c r="C25" s="32">
-        <f>+VLOOKUP($A25,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>3</v>
-      </c>
-      <c r="D25" s="33" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="32">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B26" s="32" t="str">
-        <f>+VLOOKUP($A26,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>accessible by public transport</v>
-      </c>
-      <c r="C26" s="32">
-        <f>+VLOOKUP($A26,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>2</v>
-      </c>
-      <c r="D26" s="33" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="32">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B27" s="32" t="str">
-        <f>+VLOOKUP($A27,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>accommodation quality</v>
-      </c>
-      <c r="C27" s="32">
-        <f>+VLOOKUP($A27,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>2</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="32">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B28" s="32" t="str">
-        <f>+VLOOKUP($A28,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>city’s accessibility</v>
-      </c>
-      <c r="C28" s="32">
-        <f>+VLOOKUP($A28,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>2</v>
-      </c>
-      <c r="D28" s="33" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="32">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B29" s="32" t="str">
-        <f>+VLOOKUP($A29,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>genuine online recommendations</v>
-      </c>
-      <c r="C29" s="32">
-        <f>+VLOOKUP($A29,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>2</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="32">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B30" s="32" t="str">
-        <f>+VLOOKUP($A30,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>hiking trails</v>
-      </c>
-      <c r="C30" s="32">
-        <f>+VLOOKUP($A30,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>2</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A31" s="32">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B31" s="32" t="str">
-        <f>+VLOOKUP($A31,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>local friendliness</v>
-      </c>
-      <c r="C31" s="32">
-        <f>+VLOOKUP($A31,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>2</v>
-      </c>
-      <c r="D31" s="33" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A32" s="32">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B32" s="32" t="str">
-        <f>+VLOOKUP($A32,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>popular city</v>
-      </c>
-      <c r="C32" s="32">
-        <f>+VLOOKUP($A32,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>2</v>
-      </c>
-      <c r="D32" s="33" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A33" s="32">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="B33" s="32" t="str">
-        <f>+VLOOKUP($A33,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>variety of hours for transportation</v>
-      </c>
-      <c r="C33" s="32">
-        <f>+VLOOKUP($A33,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>2</v>
-      </c>
-      <c r="D33" s="33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A34" s="32">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B34" s="32" t="str">
-        <f>+VLOOKUP($A34,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>access to mountains</v>
-      </c>
-      <c r="C34" s="32">
-        <f>+VLOOKUP($A34,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D34" s="33" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A35" s="32">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B35" s="32" t="str">
-        <f>+VLOOKUP($A35,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>attraction availability</v>
-      </c>
-      <c r="C35" s="32">
-        <f>+VLOOKUP($A35,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D35" s="33" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A36" s="32">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="B36" s="32" t="str">
-        <f>+VLOOKUP($A36,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>availability of city tours</v>
-      </c>
-      <c r="C36" s="32">
-        <f>+VLOOKUP($A36,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D36" s="33" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A37" s="32">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="B37" s="32" t="str">
-        <f>+VLOOKUP($A37,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>availability of travel agencies</v>
-      </c>
-      <c r="C37" s="32">
-        <f>+VLOOKUP($A37,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D37" s="33" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A38" s="32">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B38" s="32" t="str">
-        <f>+VLOOKUP($A38,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>car friendly</v>
-      </c>
-      <c r="C38" s="32">
-        <f>+VLOOKUP($A38,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D38" s="33" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A39" s="32">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B39" s="32" t="str">
-        <f>+VLOOKUP($A39,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>destination size</v>
-      </c>
-      <c r="C39" s="32">
-        <f>+VLOOKUP($A39,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D39" s="33" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A40" s="32">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="B40" s="32" t="str">
-        <f>+VLOOKUP($A40,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>events price</v>
-      </c>
-      <c r="C40" s="32">
-        <f>+VLOOKUP($A40,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D40" s="33" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A41" s="32">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="B41" s="32" t="str">
-        <f>+VLOOKUP($A41,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>local experience</v>
-      </c>
-      <c r="C41" s="32">
-        <f>+VLOOKUP($A41,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D41" s="33" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A42" s="32">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="B42" s="32" t="str">
-        <f>+VLOOKUP($A42,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>local restaurants</v>
-      </c>
-      <c r="C42" s="32">
-        <f>+VLOOKUP($A42,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D42" s="33" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A43" s="32">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B43" s="32" t="str">
-        <f>+VLOOKUP($A43,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>music events</v>
-      </c>
-      <c r="C43" s="32">
-        <f>+VLOOKUP($A43,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D43" s="33" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A44" s="32">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B44" s="32" t="str">
-        <f>+VLOOKUP($A44,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>music events cost</v>
-      </c>
-      <c r="C44" s="32">
-        <f>+VLOOKUP($A44,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D44" s="33" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A45" s="34">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B45" s="34" t="str">
-        <f>+VLOOKUP($A45,Attributes_by_Interview!$A:$C,2,0)</f>
-        <v>supermarket availability</v>
-      </c>
-      <c r="C45" s="34">
-        <f>+VLOOKUP($A45,Attributes_by_Interview!$A:$C,3,0)</f>
-        <v>1</v>
-      </c>
-      <c r="D45" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
